--- a/BVSimulationFiles/88.xlsx
+++ b/BVSimulationFiles/88.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005088105726872246</v>
+        <v>0.001017621145374449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005150707164386738</v>
+        <v>0.001030141432877348</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005213308601901229</v>
+        <v>0.001042661720380246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005275910039415719</v>
+        <v>0.001055182007883144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000533851147693021</v>
+        <v>0.001067702295386042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005401112914444702</v>
+        <v>0.00108022258288894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005463714351959194</v>
+        <v>0.001092742870391839</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005526315789473684</v>
+        <v>0.001105263157894737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005588917226988175</v>
+        <v>0.001117783445397635</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005651518664502666</v>
+        <v>0.001130303732900533</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005714120102017158</v>
+        <v>0.001142824020403432</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0005776721539531648</v>
+        <v>0.00115534430790633</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005839322977046139</v>
+        <v>0.001167864595409228</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000590192441456063</v>
+        <v>0.001180384882912126</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005964525852075121</v>
+        <v>0.001192905170415024</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006027127289589613</v>
+        <v>0.001205425457917923</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006089728727104104</v>
+        <v>0.001217945745420821</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006152330164618595</v>
+        <v>0.001230466032923719</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006214931602133086</v>
+        <v>0.001242986320426617</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006277533039647578</v>
+        <v>0.001255506607929516</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005088105726872246</v>
+        <v>0.001017621145374449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005150707164386738</v>
+        <v>0.001030141432877348</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005213308601901229</v>
+        <v>0.001042661720380246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005275910039415719</v>
+        <v>0.001055182007883144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000533851147693021</v>
+        <v>0.001067702295386042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005401112914444702</v>
+        <v>0.00108022258288894</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005463714351959194</v>
+        <v>0.001092742870391839</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005526315789473684</v>
+        <v>0.001105263157894737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005588917226988175</v>
+        <v>0.001117783445397635</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005651518664502666</v>
+        <v>0.001130303732900533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005714120102017158</v>
+        <v>0.001142824020403432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005776721539531648</v>
+        <v>0.00115534430790633</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005839322977046139</v>
+        <v>0.001167864595409228</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000590192441456063</v>
+        <v>0.001180384882912126</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005964525852075121</v>
+        <v>0.001192905170415024</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006027127289589613</v>
+        <v>0.001205425457917923</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006089728727104104</v>
+        <v>0.001217945745420821</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006152330164618595</v>
+        <v>0.001230466032923719</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006214931602133086</v>
+        <v>0.001242986320426617</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006277533039647578</v>
+        <v>0.001255506607929516</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/88.xlsx
+++ b/BVSimulationFiles/88.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001017621145374449</v>
+        <v>0.01017621145374449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001030141432877348</v>
+        <v>0.01030141432877348</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001042661720380246</v>
+        <v>0.01042661720380246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001055182007883144</v>
+        <v>0.01055182007883144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001067702295386042</v>
+        <v>0.01067702295386042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00108022258288894</v>
+        <v>0.0108022258288894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001092742870391839</v>
+        <v>0.01092742870391839</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001105263157894737</v>
+        <v>0.01105263157894737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001117783445397635</v>
+        <v>0.01117783445397635</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001130303732900533</v>
+        <v>0.01130303732900533</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001142824020403432</v>
+        <v>0.01142824020403432</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00115534430790633</v>
+        <v>0.0115534430790633</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001167864595409228</v>
+        <v>0.01167864595409228</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001180384882912126</v>
+        <v>0.01180384882912126</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001192905170415024</v>
+        <v>0.01192905170415024</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001205425457917923</v>
+        <v>0.01205425457917923</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001217945745420821</v>
+        <v>0.01217945745420821</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001230466032923719</v>
+        <v>0.01230466032923719</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001242986320426617</v>
+        <v>0.01242986320426617</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001255506607929516</v>
+        <v>0.01255506607929516</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001017621145374449</v>
+        <v>0.01017621145374449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001030141432877348</v>
+        <v>0.01030141432877348</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001042661720380246</v>
+        <v>0.01042661720380246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001055182007883144</v>
+        <v>0.01055182007883144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001067702295386042</v>
+        <v>0.01067702295386042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00108022258288894</v>
+        <v>0.0108022258288894</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001092742870391839</v>
+        <v>0.01092742870391839</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001105263157894737</v>
+        <v>0.01105263157894737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001117783445397635</v>
+        <v>0.01117783445397635</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001130303732900533</v>
+        <v>0.01130303732900533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001142824020403432</v>
+        <v>0.01142824020403432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00115534430790633</v>
+        <v>0.0115534430790633</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001167864595409228</v>
+        <v>0.01167864595409228</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001180384882912126</v>
+        <v>0.01180384882912126</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001192905170415024</v>
+        <v>0.01192905170415024</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001205425457917923</v>
+        <v>0.01205425457917923</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001217945745420821</v>
+        <v>0.01217945745420821</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001230466032923719</v>
+        <v>0.01230466032923719</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001242986320426617</v>
+        <v>0.01242986320426617</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001255506607929516</v>
+        <v>0.01255506607929516</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/88.xlsx
+++ b/BVSimulationFiles/88.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.001988421052631579</v>
+        <v>0.001302758620689655</v>
       </c>
       <c r="D1" t="n">
-        <v>0.003976842105263158</v>
+        <v>0.002605517241379311</v>
       </c>
       <c r="E1" t="n">
-        <v>0.005965263157894737</v>
+        <v>0.003908275862068966</v>
       </c>
       <c r="F1" t="n">
-        <v>0.007953684210526316</v>
+        <v>0.005211034482758621</v>
       </c>
       <c r="G1" t="n">
-        <v>0.009942105263157896</v>
+        <v>0.006513793103448275</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01193052631578947</v>
+        <v>0.007816551724137932</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01391894736842105</v>
+        <v>0.009119310344827587</v>
       </c>
       <c r="J1" t="n">
-        <v>0.01590736842105263</v>
+        <v>0.01042206896551724</v>
       </c>
       <c r="K1" t="n">
-        <v>0.01789578947368421</v>
+        <v>0.0117248275862069</v>
       </c>
       <c r="L1" t="n">
-        <v>0.01988421052631579</v>
+        <v>0.01302758620689655</v>
       </c>
       <c r="M1" t="n">
-        <v>0.02187263157894737</v>
+        <v>0.01433034482758621</v>
       </c>
       <c r="N1" t="n">
-        <v>0.02386105263157895</v>
+        <v>0.01563310344827586</v>
       </c>
       <c r="O1" t="n">
-        <v>0.02584947368421053</v>
+        <v>0.01693586206896552</v>
       </c>
       <c r="P1" t="n">
-        <v>0.02783789473684211</v>
+        <v>0.01823862068965517</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.02982631578947369</v>
+        <v>0.01954137931034483</v>
       </c>
       <c r="R1" t="n">
-        <v>0.03181473684210526</v>
+        <v>0.02084413793103448</v>
       </c>
       <c r="S1" t="n">
-        <v>0.03380315789473684</v>
+        <v>0.02214689655172414</v>
       </c>
       <c r="T1" t="n">
-        <v>0.03579157894736842</v>
+        <v>0.02344965517241379</v>
       </c>
       <c r="U1" t="n">
+        <v>0.02475241379310345</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.0260551724137931</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.02735793103448276</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.02866068965517242</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.02996344827586207</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.03126620689655173</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.03256896551724138</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.03387172413793103</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.03517448275862069</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.03647724137931035</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.03778</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01017621145374449</v>
+        <v>0.03567388446722022</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01030141432877348</v>
+        <v>0.03596144824707243</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01042661720380246</v>
+        <v>0.03624901202692463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01055182007883144</v>
+        <v>0.03653657580677683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01067702295386042</v>
+        <v>0.03682413958662903</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0108022258288894</v>
+        <v>0.03711170336648123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01092742870391839</v>
+        <v>0.03739926714633343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01105263157894737</v>
+        <v>0.03768683092618564</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01117783445397635</v>
+        <v>0.03797439470603783</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01130303732900533</v>
+        <v>0.03826195848589004</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01142824020403432</v>
+        <v>0.03854952226574224</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0115534430790633</v>
+        <v>0.03883708604559444</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01167864595409228</v>
+        <v>0.03912464982544664</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01180384882912126</v>
+        <v>0.03941221360529884</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01192905170415024</v>
+        <v>0.03969977738515104</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01205425457917923</v>
+        <v>0.03998734116500324</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01217945745420821</v>
+        <v>0.04027490494485544</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01230466032923719</v>
+        <v>0.04056246872470764</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01242986320426617</v>
+        <v>0.04085003250455985</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01255506607929516</v>
+        <v>0.04113759628441204</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.04142516006426424</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.04171272384411644</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.04200028762396864</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.04228785140382085</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.04257541518367305</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.04286297896352525</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.04315054274337744</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.04343810652322965</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.04372567030308185</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.04401323408293405</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01017621145374449</v>
+        <v>0.03567388446722022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01030141432877348</v>
+        <v>0.03596144824707243</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01042661720380246</v>
+        <v>0.03624901202692463</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01055182007883144</v>
+        <v>0.03653657580677683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01067702295386042</v>
+        <v>0.03682413958662903</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0108022258288894</v>
+        <v>0.03711170336648123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01092742870391839</v>
+        <v>0.03739926714633343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01105263157894737</v>
+        <v>0.03768683092618564</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01117783445397635</v>
+        <v>0.03797439470603783</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01130303732900533</v>
+        <v>0.03826195848589004</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01142824020403432</v>
+        <v>0.03854952226574224</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0115534430790633</v>
+        <v>0.03883708604559444</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01167864595409228</v>
+        <v>0.03912464982544664</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01180384882912126</v>
+        <v>0.03941221360529884</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01192905170415024</v>
+        <v>0.03969977738515104</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01205425457917923</v>
+        <v>0.03998734116500324</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01217945745420821</v>
+        <v>0.04027490494485544</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01230466032923719</v>
+        <v>0.04056246872470764</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01242986320426617</v>
+        <v>0.04085003250455985</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01255506607929516</v>
+        <v>0.04113759628441204</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04142516006426424</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.04171272384411644</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.04200028762396864</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04228785140382085</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.04257541518367305</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.04286297896352525</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.04315054274337744</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.04343810652322965</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.04372567030308185</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04401323408293405</v>
       </c>
     </row>
   </sheetData>
